--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/Parirenyatwa Group of Hospitals Admission - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/Parirenyatwa Group of Hospitals Admission - metadata.xlsx
@@ -1668,7 +1668,7 @@
         <v/>
       </c>
       <c r="O19" t="str">
-        <v>($NoPulseOx = false and $SatsAir &lt; 90) or ($NoPulseOx = false and $RR &gt; 60)</v>
+        <v>$SatsAir &lt; 90 or $RR &gt; 60</v>
       </c>
       <c r="P19" t="str">
         <v/>
@@ -2596,7 +2596,7 @@
         <v>BloodSugarmmol</v>
       </c>
       <c r="G33" t="str">
-        <v>Blood Sugar (mmol/L)      (2.5 - 4.5)</v>
+        <v>Blood Sugar (mmol/L)      (2.6 - 8.3)</v>
       </c>
       <c r="H33" t="str">
         <v>number</v>
@@ -2750,13 +2750,13 @@
         <v>No</v>
       </c>
       <c r="M35" t="str">
-        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 46.8</v>
+        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 47</v>
       </c>
       <c r="N35" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O35" t="str">
-        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 46.8</v>
+        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 47</v>
       </c>
       <c r="P35" t="str">
         <v/>
@@ -2957,7 +2957,7 @@
         <v/>
       </c>
       <c r="N38" t="str">
-        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Convulsions","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty in breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"FD","valueLabel":"Not sucking / feeding difficulties"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"NE","valueLabel":"Neonatal encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LowBirthWeight","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium Aspiration"},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida"},{"value":"Prem","valueLabel":"Prematurity"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Severe Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Other congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Suspected neonatal sepsis"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Convulsions","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty in breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"FD","valueLabel":"Not sucking / feeding difficulties"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"NE","valueLabel":"Neonatal encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LowBirthWeight","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium Aspiration"},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida"},{"value":"Prem","valueLabel":"Premature"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Severe Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Other congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Sepsis suspected"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -3025,7 +3025,7 @@
         <v/>
       </c>
       <c r="N39" t="str">
-        <v>[{"value":"Cong","valueLabel":"Other Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AD","valueLabel":"Abdominal distension","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fev","valueLabel":"Fever","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic ischaemic encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVX","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low birth weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mec","valueLabel":"Possible Meconium aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OM","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pneum","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"Cong","valueLabel":"Other Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AD","valueLabel":"Abdominal distension","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fev","valueLabel":"Fever","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic ischaemic encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVX","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low birth weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mec","valueLabel":"Possible Meconium aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OM","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pneum","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -3226,7 +3226,7 @@
         <v>No</v>
       </c>
       <c r="M42" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!(($AdmReason = 'DU') or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N42" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
@@ -3362,7 +3362,7 @@
         <v>No</v>
       </c>
       <c r="M44" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N44" t="str">
         <v/>
@@ -3430,7 +3430,7 @@
         <v>No</v>
       </c>
       <c r="M45" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N45" t="str">
         <v/>
@@ -3498,7 +3498,7 @@
         <v>Yes</v>
       </c>
       <c r="M46" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N46" t="str">
         <v/>
@@ -3566,7 +3566,7 @@
         <v>No</v>
       </c>
       <c r="M47" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N47" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
@@ -3702,7 +3702,7 @@
         <v>No</v>
       </c>
       <c r="M49" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N49" t="str">
         <v>[{"value":"PNWG","valueLabel":"Post Natal Ward (ground floor)"},{"value":"PNW1","valueLabel":"Post Natal Ward (1st floor)"},{"value":"ELW","valueLabel":"Early Labour Ward (1st floor)"},{"value":"ICU","valueLabel":"⁠B7 ICU (main hospital)"},{"value":"GW","valueLabel":"Gynaecology Ward (main hospital)"},{"value":"MW","valueLabel":"Medical Wards (main hospital)"},{"value":"NA","valueLabel":"Not Admitted"}]</v>
@@ -3770,7 +3770,7 @@
         <v>Yes</v>
       </c>
       <c r="M50" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N50" t="str">
         <v/>
@@ -3838,7 +3838,7 @@
         <v>Yes</v>
       </c>
       <c r="M51" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N51" t="str">
         <v/>
@@ -3906,7 +3906,7 @@
         <v>Yes</v>
       </c>
       <c r="M52" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N52" t="str">
         <v/>
@@ -4246,7 +4246,7 @@
         <v>No</v>
       </c>
       <c r="M57" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N57" t="str">
         <v/>
@@ -4568,7 +4568,7 @@
         <v>Gestation</v>
       </c>
       <c r="G62" t="str">
-        <v>Gestational age at birth (weeks.days)</v>
+        <v>Estimated Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H62" t="str">
         <v>number</v>
@@ -4586,7 +4586,7 @@
         <v>No</v>
       </c>
       <c r="M62" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N62" t="str">
         <v/>
@@ -4654,7 +4654,7 @@
         <v>No</v>
       </c>
       <c r="M63" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N63" t="str">
         <v>[{"value":"EUSS","valueLabel":"Early Ultrasound (less than 14 weeks)"},{"value":"IVF","valueLabel":"IVF pregnancy"},{"value":"LMP","valueLabel":"Last Menstrual Period (LMP)"},{"value":"FH","valueLabel":"Fundal height"},{"value":"Oth","valueLabel":"Other"},{"value":"Unk","valueLabel":"Unknown"}]</v>
@@ -4722,7 +4722,7 @@
         <v>No</v>
       </c>
       <c r="M64" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N64" t="str">
         <v>[{"value":"S","valueLabel":"Single"},{"value":"Tw1","valueLabel":"1st Twin"},{"value":"Tw2","valueLabel":"2nd Twin"},{"value":"Tr1","valueLabel":"1st Triplet"},{"value":"Tr2","valueLabel":"2nd Triplet"},{"value":"Tr3","valueLabel":"3rd Triplet"}]</v>
@@ -4790,7 +4790,7 @@
         <v>No</v>
       </c>
       <c r="M65" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N65" t="str">
         <v/>
@@ -4858,7 +4858,7 @@
         <v>No</v>
       </c>
       <c r="M66" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N66" t="str">
         <v/>
@@ -4926,7 +4926,7 @@
         <v>No</v>
       </c>
       <c r="M67" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N67" t="str">
         <v/>
@@ -4994,7 +4994,7 @@
         <v>No</v>
       </c>
       <c r="M68" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N68" t="str">
         <v/>
@@ -5062,7 +5062,7 @@
         <v>No</v>
       </c>
       <c r="M69" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N69" t="str">
         <v/>
@@ -5130,7 +5130,7 @@
         <v>No</v>
       </c>
       <c r="M70" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N70" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -5198,7 +5198,7 @@
         <v>No</v>
       </c>
       <c r="M71" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N71" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
@@ -5402,13 +5402,13 @@
         <v>No</v>
       </c>
       <c r="M74" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N74" t="str">
         <v>[{"value":"ALC","valueLabel":"Alcohol","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TOB","valueLabel":"Tobacco","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DRUG","valueLabel":"Illicit Drugs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O74" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P74" t="str">
         <v/>
@@ -5810,7 +5810,7 @@
         <v>No</v>
       </c>
       <c r="M80" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N80" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Known"}]</v>
@@ -6082,7 +6082,7 @@
         <v>No</v>
       </c>
       <c r="M84" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N84" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -6150,7 +6150,7 @@
         <v>No</v>
       </c>
       <c r="M85" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N85" t="str">
         <v>[{"value":"1","valueLabel":"Spontaneous Vaginal Delivery"},{"value":"7","valueLabel":"Induced Vaginal Delivery"},{"value":"6","valueLabel":"Breech extraction (vaginal)"},{"value":"2","valueLabel":"Vacuum extraction"},{"value":"3","valueLabel":"Forceps extraction"},{"value":"4","valueLabel":"Elective Ceasarian Section (ELCS)"},{"value":"5","valueLabel":"Emergency Ceasarian Section (EMCS)"}]</v>
@@ -6218,7 +6218,7 @@
         <v>No</v>
       </c>
       <c r="M86" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N86" t="str">
         <v>[{"value":"Vertex","valueLabel":"Vertex"},{"value":"Brow","valueLabel":"Brow"},{"value":"Breech","valueLabel":"Breech"},{"value":"Face","valueLabel":"Face"},{"value":"Unk","valueLabel":"Unknown"}]</v>
@@ -6422,7 +6422,7 @@
         <v>No</v>
       </c>
       <c r="M89" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N89" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
@@ -6762,7 +6762,7 @@
         <v>No</v>
       </c>
       <c r="M94" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N94" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -6898,7 +6898,7 @@
         <v>No</v>
       </c>
       <c r="M96" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N96" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -6966,7 +6966,7 @@
         <v>No</v>
       </c>
       <c r="M97" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N97" t="str">
         <v>[{"value":"Y","valueLabel":"yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -7034,7 +7034,7 @@
         <v>No</v>
       </c>
       <c r="M98" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N98" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -7170,7 +7170,7 @@
         <v>No</v>
       </c>
       <c r="M100" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N100" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -7306,7 +7306,7 @@
         <v>No</v>
       </c>
       <c r="M102" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N102" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -7578,7 +7578,7 @@
         <v>Yes</v>
       </c>
       <c r="M106" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N106" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -7646,7 +7646,7 @@
         <v>No</v>
       </c>
       <c r="M107" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N107" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NS","valueLabel":"Not Sure"}]</v>
@@ -7714,7 +7714,7 @@
         <v>No</v>
       </c>
       <c r="M108" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N108" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NS","valueLabel":"Not Sure"}]</v>
@@ -7782,7 +7782,7 @@
         <v>No</v>
       </c>
       <c r="M109" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N109" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -7850,7 +7850,7 @@
         <v>No</v>
       </c>
       <c r="M110" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N110" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -7918,7 +7918,7 @@
         <v>No</v>
       </c>
       <c r="M111" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N111" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -7986,7 +7986,7 @@
         <v>No</v>
       </c>
       <c r="M112" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N112" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -8054,7 +8054,7 @@
         <v>No</v>
       </c>
       <c r="M113" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N113" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -9553,7 +9553,7 @@
         <v/>
       </c>
       <c r="N135" t="str">
-        <v>[{"value":"0","valueLabel":"None"},{"value":"1","valueLabel":"Mild"},{"value":"2","valueLabel":"Severe"}]</v>
+        <v>[{"value":"1","valueLabel":"Mild"},{"value":"2","valueLabel":"Severe"}]</v>
       </c>
       <c r="O135" t="str">
         <v>$RR &gt; 60 or $DangerSigns = 'Grun' or $DangerSigns = 'Cyan' or $SatsAIr &lt; 90 or $SatsO2 &lt; 90 or $RespSR = 'DIB' or $RespSR = 'BE' or $RespSR = 'Apn' or $RespSR = 'Cough' or $RespSR = 'NBr' or $SignsRD = 'TT' or $SignsRD = 'NFL' or $SignsRD = 'CHI' or $SignsRD = 'HN' or $SignsRD = 'ST' or $SignsRD = 'GR' or $SignsRD = 'Gasp' or $SignsRD = 'GR'</v>
@@ -9621,7 +9621,7 @@
         <v/>
       </c>
       <c r="N136" t="str">
-        <v>[{"value":"0","valueLabel":"None"},{"value":"1","valueLabel":"Cyanosis relieved by O2"},{"value":"2","valueLabel":"Cyanosis NOT relieved by O2"}]</v>
+        <v>[{"value":"0","valueLabel":" None"},{"value":"1","valueLabel":" Cyanosis relieved by O2"},{"value":"2","valueLabel":" Cyanosis NOT relieved by O2"}]</v>
       </c>
       <c r="O136" t="str">
         <v>$RR &gt; 60 or $DangerSigns = 'Grun' or $DangerSigns = 'Cyan' or $SatsAIr &lt; 90 or $SatsO2 &lt; 90 or $RespSR = 'DIB' or $RespSR = 'BE' or $RespSR = 'Apn' or $RespSR = 'Cough' or $RespSR = 'NBr' or $SignsRD = 'TT' or $SignsRD = 'NFL' or $SignsRD = 'CHI' or $SignsRD = 'HN' or $SignsRD = 'ST' or $SignsRD = 'GR' or $SignsRD = 'Gasp' or $SignsRD = 'GR'</v>
@@ -9665,7 +9665,7 @@
         <v>form</v>
       </c>
       <c r="F137" t="str">
-        <v>AirEntry</v>
+        <v>AirEntDwn</v>
       </c>
       <c r="G137" t="str">
         <v>Air Entry</v>
@@ -9757,7 +9757,7 @@
         <v/>
       </c>
       <c r="N138" t="str">
-        <v>[{"value":"0","valueLabel":"None"},{"value":"1","valueLabel":"Audible with stethoscope"},{"value":"2","valueLabel":"Audible with ear"}]</v>
+        <v>[{"value":"1","valueLabel":"Audible with stethoscope"},{"value":"2","valueLabel":"Audible with ear"}]</v>
       </c>
       <c r="O138" t="str">
         <v>$RR &gt; 60 or $DangerSigns = 'Grun' or $DangerSigns = 'Cyan' or $SatsAIr &lt; 90 or $SatsO2 &lt; 90 or $RespSR = 'DIB' or $RespSR = 'BE' or $RespSR = 'Apn' or $RespSR = 'Cough' or $RespSR = 'NBr' or $SignsRD = 'TT' or $SignsRD = 'NFL' or $SignsRD = 'CHI' or $SignsRD = 'HN' or $SignsRD = 'ST' or $SignsRD = 'GR' or $SignsRD = 'Gasp' or $SignsRD = 'GR'</v>
@@ -11525,7 +11525,7 @@
         <v>$FeverSR = true</v>
       </c>
       <c r="N164" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O164" t="str">
         <v>$FeverSR = true</v>
@@ -11661,7 +11661,7 @@
         <v>$RespSR != 'Norm'</v>
       </c>
       <c r="N166" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O166" t="str">
         <v>$RespSR != 'Norm'</v>
@@ -11797,7 +11797,7 @@
         <v>$Vomiting != 'Norm'</v>
       </c>
       <c r="N168" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O168" t="str">
         <v>$Vomiting != 'Norm'</v>
@@ -12137,7 +12137,7 @@
         <v>$Age &gt; 47.9 or $AgeEstimate = 'INF72' or $AgeEstimate = 'INF'</v>
       </c>
       <c r="N173" t="str">
-        <v>[{"value":"Norm","valueLabel":"Passing urine normally"},{"value":"NoPU","valueLabel":"Not passing urine"}]</v>
+        <v>[{"value":"Norm","valueLabel":"Passing urine normally"}]</v>
       </c>
       <c r="O173" t="str">
         <v/>
@@ -12273,7 +12273,7 @@
         <v>$SRNeuroOther != 'Norm'</v>
       </c>
       <c r="N175" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O175" t="str">
         <v>$SRNeuroOther != 'Norm'</v>
@@ -12344,7 +12344,7 @@
         <v>[{"value":"HA","valueLabel":"Harare"},{"value":"BU","valueLabel":"Bulawayo"},{"value":"MC","valueLabel":"Mashonaland Central"},{"value":"ME","valueLabel":"Mashonaland East"},{"value":"MW","valueLabel":"Mashonaland West"},{"value":"MA","valueLabel":"Manicaland"},{"value":"MAS","valueLabel":"Masvingo"},{"value":"MN","valueLabel":"Matabeleland North"},{"value":"MS","valueLabel":"Matabeleland South"},{"value":"MID","valueLabel":"Midlands"}]</v>
       </c>
       <c r="O176" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P176" t="str">
         <v/>
@@ -12412,7 +12412,7 @@
         <v/>
       </c>
       <c r="O177" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P177" t="str">
         <v/>
@@ -12480,7 +12480,7 @@
         <v/>
       </c>
       <c r="O178" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P178" t="str">
         <v/>
@@ -12548,7 +12548,7 @@
         <v/>
       </c>
       <c r="O179" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P179" t="str">
         <v/>
@@ -12616,7 +12616,7 @@
         <v/>
       </c>
       <c r="O180" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P180" t="str">
         <v/>
@@ -12746,13 +12746,13 @@
         <v>No</v>
       </c>
       <c r="M182" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N182" t="str">
         <v>[{"value":"MAR","valueLabel":"Married","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DIV","valueLabel":"Divorced","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"WID","valueLabel":"Widowed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Single","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O182" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P182" t="str">
         <v/>
@@ -12820,7 +12820,7 @@
         <v>[{"value":"A","valueLabel":"African"},{"value":"AA","valueLabel":"African American"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O183" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P183" t="str">
         <v/>
@@ -12888,7 +12888,7 @@
         <v/>
       </c>
       <c r="O184" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P184" t="str">
         <v/>
@@ -12950,13 +12950,13 @@
         <v>No</v>
       </c>
       <c r="M185" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N185" t="str">
         <v>[{"value":"CH","valueLabel":"Christian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MU","valueLabel":"Muslim","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATR","valueLabel":"African Traditional Religion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AS","valueLabel":"Apostolic Sect","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"JW","valueLabel":"Jehovah's Witness","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATH","valueLabel":"Atheist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O185" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P185" t="str">
         <v/>
@@ -13086,13 +13086,13 @@
         <v>No</v>
       </c>
       <c r="M187" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N187" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O187" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P187" t="str">
         <v/>
@@ -13219,7 +13219,7 @@
         <v>Yes</v>
       </c>
       <c r="L189" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M189" t="str">
         <v/>
@@ -13361,7 +13361,7 @@
         <v/>
       </c>
       <c r="N191" t="str">
-        <v>[{"value":"R","valueLabel":"Positive"},{"value":"NR","valueLabel":"Negative"},{"value":"U","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"R","valueLabel":"Positive"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O191" t="str">
         <v>$MatHIVtest = true</v>
@@ -13473,10 +13473,10 @@
         <v>form</v>
       </c>
       <c r="F193" t="str">
-        <v>HAART</v>
+        <v>MaHAART</v>
       </c>
       <c r="G193" t="str">
-        <v>Maternal HAART Status</v>
+        <v>Is the mother on HAART?</v>
       </c>
       <c r="H193" t="str">
         <v>dropdown</v>
@@ -13544,7 +13544,7 @@
         <v>LengthHAART</v>
       </c>
       <c r="G194" t="str">
-        <v>Mother on HAART since when?</v>
+        <v>Maternal HAART Initiation</v>
       </c>
       <c r="H194" t="str">
         <v>dropdown</v>
@@ -13562,7 +13562,7 @@
         <v>No</v>
       </c>
       <c r="M194" t="str">
-        <v>$HAART = 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N194" t="str">
         <v>[{"value":"1stTrim","valueLabel":"1st Trimester or earlier"},{"value":"2ndTrim","valueLabel":"2nd Trimester"},{"value":"3rdTrim","valueLabel":"3rd Trimester more than 1 month before delivery"},{"value":"Late","valueLabel":"Less than 1 month before delivery"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -13630,7 +13630,7 @@
         <v>No</v>
       </c>
       <c r="M195" t="str">
-        <v>$HAART= 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N195" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NA","valueLabel":"Not applicable"}]</v>
@@ -13680,7 +13680,7 @@
         <v>VLNumber</v>
       </c>
       <c r="G196" t="str">
-        <v>Viral Load</v>
+        <v>Viral Load (copies/ml)</v>
       </c>
       <c r="H196" t="str">
         <v>number</v>
@@ -13970,13 +13970,13 @@
         <v>No</v>
       </c>
       <c r="M200" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N200" t="str">
         <v>[{"value":"Y","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O200" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P200" t="str">
         <v/>
@@ -14514,13 +14514,13 @@
         <v>No</v>
       </c>
       <c r="M208" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N208" t="str">
         <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DM","valueLabel":"Diabetes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HD","valueLabel":"Heart disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HTN","valueLabel":"Hypertension or pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malaria","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"STD","valueLabel":"Sexually Transmitted Disease (other than HIV/syphilis)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"THY","valueLabel":"Thyroid disease / goitre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TU","valueLabel":"Tuberculosis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Unknown","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O208" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P208" t="str">
         <v/>
@@ -14724,7 +14724,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O211" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P211" t="str">
         <v/>
@@ -14792,7 +14792,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O212" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P212" t="str">
         <v/>
@@ -14860,7 +14860,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O213" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P213" t="str">
         <v/>
@@ -14922,13 +14922,13 @@
         <v>No</v>
       </c>
       <c r="M214" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N214" t="str">
         <v>[{"value":"SVB","valueLabel":"Significant Vaginal Bleeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pre","valueLabel":"Pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions / Eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CordProl","valueLabel":"Cord Prolapse","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Abr","valueLabel":"Abruption","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Poly","valueLabel":"Polyhydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Olig","valueLabel":"Oligohydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O214" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P214" t="str">
         <v/>
@@ -15398,13 +15398,13 @@
         <v>No</v>
       </c>
       <c r="M221" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N221" t="str">
-        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O221" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P221" t="str">
         <v/>
@@ -16421,7 +16421,7 @@
         <v/>
       </c>
       <c r="N236" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Omph","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftLip","valueLabel":"Cleft lip","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftPal","valueLabel":"Cleft palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Myelo","valueLabel":"Myelomeningocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Possible Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVU","valueLabel":"HIV Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHypo","valueLabel":"Severe Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ModHypo","valueLabel":"Moderate Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiHypo","valueLabel":"Mild Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Hyperth","valueLabel":"Hyperthermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DJ","valueLabel":"Pathological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MJ","valueLabel":"Physiological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ProJ","valueLabel":"Prolonged Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature (32-36 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia /  Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NSep","valueLabel":"Suspected neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Risk","valueLabel":"Risk factors for sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BI","valueLabel":"Birth Trauma","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dhyd","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DUM","valueLabel":"Abandoned baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Safe","valueLabel":"Safekeeping","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NB","valueLabel":"Normal Baby","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVExp","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Omph","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftLip","valueLabel":"Cleft lip","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftPal","valueLabel":"Cleft palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Myelo","valueLabel":"Myelomeningocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Possible Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVU","valueLabel":"HIV Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHypo","valueLabel":"Severe Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ModHypo","valueLabel":"Moderate Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiHypo","valueLabel":"Mild Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Hyperth","valueLabel":"Hyperthermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DJ","valueLabel":"Pathological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MJ","valueLabel":"Physiological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ProJ","valueLabel":"Prolonged Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature (32-36 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia /  Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NSep","valueLabel":"Suspected neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Risk","valueLabel":"Risk factors for sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BT","valueLabel":"Birth injury / Trauma","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born before arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dhyd","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DUM","valueLabel":"Abandoned baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Safe","valueLabel":"Safekeeping","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NB","valueLabel":"Normal Baby","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVExp","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O236" t="str">
         <v/>
@@ -16492,7 +16492,7 @@
         <v/>
       </c>
       <c r="O237" t="str">
-        <v>($DangerSigns = 'Grun' or $RR &gt; 60 or $SatsO2 &lt; 90 or $WOB = 'Mod' or $WOB = 'Sev' or $Diagnoses = 'RDN' or $AdmReason = 'PREMRDS') and $NobCPAP = false</v>
+        <v xml:space="preserve">($DangerSigns = 'Grun' or $RR &gt; 60 or $SatsO2 &lt; 90 or $WOB = 'Mod' or $WOB = 'Sev' or $AdmReason = 'PREMRDS') </v>
       </c>
       <c r="P237" t="str">
         <v/>
@@ -16625,7 +16625,7 @@
         <v/>
       </c>
       <c r="N239" t="str">
-        <v>[{"value":"Term","valueLabel":"Admit to Term Unit","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IKMC","valueLabel":"Admit to IKMC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ICU","valueLabel":"Admit to ICU","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NICU","valueLabel":"Admit to Neonatal Intensive Care Unit","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPAP","valueLabel":"CPAP","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NC02","valueLabel":"Nasal Cannulae Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Warm","valueLabel":"Keep warm with hat, bootees etc","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Obs","valueLabel":"Observations 4 hourly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PTX","valueLabel":"Phototherapy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SBR","valueLabel":"Check bilirubin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FBC","valueLabel":"Check FBC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BC","valueLabel":"Blood culture","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Incub","valueLabel":"Incubator","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gluc","valueLabel":"Check glucose stat then 4 hourly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Renal","valueLabel":"Check renal function","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DNA","valueLabel":"DNA PCR for HIV","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BF","valueLabel":"Breast feed freely","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cup","valueLabel":"Breast feed with cup top ups","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NG","valueLabel":"Breast feed with NG top ups","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OGX","valueLabel":"OGT feed exclusively","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AMIN","valueLabel":"Aminophylline","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Amik","valueLabel":"Amikacin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gent","valueLabel":"Gentamicin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Xpen","valueLabel":"X Penicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NVP","valueLabel":"Nevirapine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Met","valueLabel":"Metronidazole","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Caff","valueLabel":"Caffeine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"TermU","valueLabel":"Term Unit","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IKMC","valueLabel":"IKMC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ICU","valueLabel":"ICU","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NICU","valueLabel":"Admit to Neonatal Intensive Care Unit","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPAP","valueLabel":"CPAP","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NC02","valueLabel":"Nasal Cannulae Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Warm","valueLabel":"Keep warm with hat, bootees etc","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Obs","valueLabel":"Observations 4 hourly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PTX","valueLabel":"Phototherapy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SBR","valueLabel":"Check bilirubin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FBC","valueLabel":"Check FBC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BC","valueLabel":"Blood culture","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Incub","valueLabel":"Incubator","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gluc","valueLabel":"Check glucose stat then 4 hourly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Renal","valueLabel":"Check renal function","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DNA","valueLabel":"DNA PCR for HIV","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BF","valueLabel":"Breast feed freely","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cup","valueLabel":"Breast feed with cup top ups","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NG","valueLabel":"Breast feed with NG top ups","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OGX","valueLabel":"OGT feed exclusively","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AMIN","valueLabel":"Aminophylline","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Amik","valueLabel":"Amikacin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gent","valueLabel":"Gentamicin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Xpen","valueLabel":"X Penicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NVP","valueLabel":"Nevirapine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Met","valueLabel":"Metronidazole","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Caff","valueLabel":"Caffeine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O239" t="str">
         <v/>
@@ -17792,7 +17792,7 @@
         <v>Parirenyatwa Group of Hospitals</v>
       </c>
       <c r="C3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="D3" t="str">
         <v>Born before arrival</v>
@@ -17804,7 +17804,7 @@
         <v>e3cb5ede-7fc1-43aa-8d79-bd36a4cd332e</v>
       </c>
       <c r="G3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="H3" t="str">
         <v>7155</v>
@@ -17849,7 +17849,7 @@
         <v>BBA</v>
       </c>
       <c r="V3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="W3" t="str">
         <v/>
@@ -17869,19 +17869,19 @@
         <v>Parirenyatwa Group of Hospitals</v>
       </c>
       <c r="C4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="D4" t="str">
         <v>Birth Trauma</v>
       </c>
       <c r="E4" t="str">
-        <v>BI</v>
+        <v>BT</v>
       </c>
       <c r="F4" t="str">
         <v>ec2adc2a-3fa6-438d-89de-7e3b87f568c6</v>
       </c>
       <c r="G4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="H4" t="str">
         <v>7156</v>
@@ -17923,10 +17923,10 @@
         <v>diagnosis</v>
       </c>
       <c r="U4" t="str">
-        <v>BI</v>
+        <v>BT</v>
       </c>
       <c r="V4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="W4" t="str">
         <v/>
@@ -19974,7 +19974,7 @@
         <v>Parirenyatwa Group of Hospitals</v>
       </c>
       <c r="C28" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="D28" t="str">
         <v>RDN - Congenital Pneumonia</v>
@@ -19986,7 +19986,7 @@
         <v>2f74e32f-d1a8-4a5a-b672-cee9b6d6fd38</v>
       </c>
       <c r="G28" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="H28" t="str">
         <v>7180</v>
@@ -20048,7 +20048,7 @@
         <v>CongPneu</v>
       </c>
       <c r="V28" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="W28" t="str">
         <v/>
@@ -22049,19 +22049,19 @@
         <v>Parirenyatwa Group of Hospitals</v>
       </c>
       <c r="C52" t="str">
-        <v>Congenital Syphilis</v>
+        <v>Congenital syphilis suspected (Exposed and symptomatic)</v>
       </c>
       <c r="D52" t="str">
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>SyphExp</v>
+        <v>CongSyph</v>
       </c>
       <c r="F52" t="str">
         <v>6f30185f-b5a7-45f4-a32c-a40881e984e0</v>
       </c>
       <c r="G52" t="str">
-        <v>Congenital Syphilis</v>
+        <v>Congenital syphilis suspected (Exposed and symptomatic)</v>
       </c>
       <c r="H52" t="str">
         <v>7204</v>
@@ -22107,10 +22107,10 @@
         <v>diagnosis</v>
       </c>
       <c r="U52" t="str">
-        <v>SyphExp</v>
+        <v>CongSyph</v>
       </c>
       <c r="V52" t="str">
-        <v>Congenital Syphilis</v>
+        <v>Congenital syphilis suspected (Exposed and symptomatic)</v>
       </c>
       <c r="W52" t="str">
         <v>$ANVDRLResult = 'P' or $AdmReason = 'Syph_Exp' or $AdmReasonAdd = 'Syph_Exp'</v>
